--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.40770758997095</v>
+        <v>9.32875248337028</v>
       </c>
       <c r="D2" t="n">
-        <v>57.39256229802831</v>
+        <v>9.326291373429601</v>
       </c>
       <c r="E2" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F2" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.58777398990195</v>
+        <v>10.82051327335907</v>
       </c>
       <c r="D3" t="n">
-        <v>67.51024274942662</v>
+        <v>10.97041444678183</v>
       </c>
       <c r="E3" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F3" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.538720513400878</v>
+        <v>0.9000420834276427</v>
       </c>
       <c r="D4" t="n">
-        <v>4.744165177318538</v>
+        <v>0.7709268413142625</v>
       </c>
       <c r="E4" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F4" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.50787787109576</v>
+        <v>8.857530154053062</v>
       </c>
       <c r="D5" t="n">
-        <v>55.40011400797436</v>
+        <v>9.002518526295834</v>
       </c>
       <c r="E5" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F5" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.77019891385573</v>
+        <v>7.437657323501556</v>
       </c>
       <c r="D6" t="n">
-        <v>46.75705972732515</v>
+        <v>7.598022205690337</v>
       </c>
       <c r="E6" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F6" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.2730956347317</v>
+        <v>5.569378040643902</v>
       </c>
       <c r="D7" t="n">
-        <v>34.9029832447081</v>
+        <v>5.671734777265065</v>
       </c>
       <c r="E7" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F7" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.48773241237748</v>
+        <v>3.97925651701134</v>
       </c>
       <c r="D8" t="n">
-        <v>25.30550692720422</v>
+        <v>4.112144875670686</v>
       </c>
       <c r="E8" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F8" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.19260106130133</v>
+        <v>6.531297672461466</v>
       </c>
       <c r="D9" t="n">
-        <v>40.12318203370595</v>
+        <v>6.520017080477217</v>
       </c>
       <c r="E9" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F9" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>81.42565180181884</v>
+        <v>13.23166841779556</v>
       </c>
       <c r="D10" t="n">
-        <v>81.02031947627232</v>
+        <v>13.16580191489425</v>
       </c>
       <c r="E10" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F10" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.87969040594346</v>
+        <v>10.05544969096581</v>
       </c>
       <c r="D11" t="n">
-        <v>61.37947915471089</v>
+        <v>9.97416536264052</v>
       </c>
       <c r="E11" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F11" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>64.9031963369778</v>
+        <v>10.54676940475889</v>
       </c>
       <c r="D12" t="n">
-        <v>65.05528201898342</v>
+        <v>10.57148332808481</v>
       </c>
       <c r="E12" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F12" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.88000305917873</v>
+        <v>7.780500497116543</v>
       </c>
       <c r="D13" t="n">
-        <v>47.19135999770635</v>
+        <v>7.668595999627282</v>
       </c>
       <c r="E13" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F13" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.48577399122512</v>
+        <v>4.303938273574083</v>
       </c>
       <c r="D14" t="n">
-        <v>25.51768957795512</v>
+        <v>4.146624556417708</v>
       </c>
       <c r="E14" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F14" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.89573999351072</v>
+        <v>7.295557748945493</v>
       </c>
       <c r="D15" t="n">
-        <v>44.64869018078117</v>
+        <v>7.255412154376939</v>
       </c>
       <c r="E15" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F15" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>82.69929479650629</v>
+        <v>13.43863540443227</v>
       </c>
       <c r="D16" t="n">
-        <v>82.05149417334869</v>
+        <v>13.33336780316916</v>
       </c>
       <c r="E16" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F16" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>47.82262317398149</v>
+        <v>7.771176265771992</v>
       </c>
       <c r="D17" t="n">
-        <v>46.88997770531095</v>
+        <v>7.619621377113029</v>
       </c>
       <c r="E17" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F17" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>37.23376354952299</v>
+        <v>6.050486576797486</v>
       </c>
       <c r="D18" t="n">
-        <v>36.28870602571616</v>
+        <v>5.896914729178876</v>
       </c>
       <c r="E18" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F18" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.43181540684881</v>
+        <v>6.245170003612931</v>
       </c>
       <c r="D19" t="n">
-        <v>37.41678802927074</v>
+        <v>6.080228054756495</v>
       </c>
       <c r="E19" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F19" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>55.35234046861937</v>
+        <v>8.994755326150649</v>
       </c>
       <c r="D20" t="n">
-        <v>54.46202471136431</v>
+        <v>8.8500790155967</v>
       </c>
       <c r="E20" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F20" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>65.42493759360039</v>
+        <v>10.63155235896006</v>
       </c>
       <c r="D21" t="n">
-        <v>64.41834812973383</v>
+        <v>10.46798157108175</v>
       </c>
       <c r="E21" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F21" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>92.06035308878326</v>
+        <v>14.95980737692728</v>
       </c>
       <c r="D22" t="n">
-        <v>91.16479140063117</v>
+        <v>14.81427860260257</v>
       </c>
       <c r="E22" t="n">
-        <v>20.29515620573697</v>
+        <v>3.297962883432258</v>
       </c>
       <c r="F22" t="n">
-        <v>20.26716270502546</v>
+        <v>3.293413939566638</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
